--- a/backtest_runs/20260410_193731/by_symbol/JDMT/JDMT.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/JDMT/JDMT.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -679,7 +679,7 @@
         <v>-10643.40000000001</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>96058</v>
@@ -771,7 +771,7 @@
         <v>-2365.200000000007</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>95357.19999999998</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>102803.2</v>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>102803.2</v>
@@ -1047,7 +1047,7 @@
         <v>-846.7999999999975</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>101956.4</v>
@@ -1139,7 +1139,7 @@
         <v>-2540.399999999992</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>99416.00000000001</v>
@@ -1231,7 +1231,7 @@
         <v>-5037.000000000005</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>97941.40000000001</v>
@@ -1277,7 +1277,7 @@
         <v>-890.5999999999992</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>97050.8</v>
@@ -1415,7 +1415,7 @@
         <v>-1737.399999999997</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>97050.8</v>
